--- a/Development/Data/Module/ModuleDataFredaP21.xlsx
+++ b/Development/Data/Module/ModuleDataFredaP21.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Basti\ARBEIT Lokal\dsFredaP21\Development\Data\PackageData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Basti\ARBEIT Lokal\dsFredaP21\Development\Data\Module\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3228D0-DFD3-4E0A-982E-C839D625F33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B777D89D-61F7-4287-BBB0-280F37098833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="724" activeTab="1" xr2:uid="{035133D3-9E9F-4CDB-BCDC-A149BB1E9383}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="724" firstSheet="5" activeTab="9" xr2:uid="{035133D3-9E9F-4CDB-BCDC-A149BB1E9383}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta.Tables" sheetId="11" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2542" uniqueCount="594">
   <si>
     <t>D</t>
   </si>
@@ -372,12 +372,6 @@
     <t>DuplicateRecords.Remove</t>
   </si>
   <si>
-    <t>FeatureAvailabilityViolations.Detect</t>
-  </si>
-  <si>
-    <t>FeatureAvailabilityViolations.Remove</t>
-  </si>
-  <si>
     <t>.DataSetRoot</t>
   </si>
   <si>
@@ -1825,6 +1819,21 @@
   </si>
   <si>
     <t>str_sub(.X, end = 2)</t>
+  </si>
+  <si>
+    <t>ValueAvailabilityViolations.Detect</t>
+  </si>
+  <si>
+    <t>ValueAvailabilityViolations.Remove</t>
+  </si>
+  <si>
+    <t>&gt;=1950-01-01</t>
+  </si>
+  <si>
+    <t>&gt;1900</t>
+  </si>
+  <si>
+    <t>ValidityCriteria</t>
   </si>
 </sst>
 </file>
@@ -2157,7 +2166,105 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="26">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2197,13 +2304,6 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2617,10 +2717,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>98</v>
@@ -2631,10 +2731,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>96</v>
@@ -2645,10 +2745,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>96</v>
@@ -2659,10 +2759,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>96</v>
@@ -2673,10 +2773,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>96</v>
@@ -2693,7 +2793,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523525EA-A817-4BE5-824B-98333B869096}">
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="25.2" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="3"/>
@@ -2702,14 +2802,15 @@
     <col min="4" max="4" width="25.88671875" style="13" customWidth="1"/>
     <col min="5" max="5" width="14.44140625" style="13" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="32.44140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" style="1"/>
-    <col min="10" max="10" width="48.21875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.21875" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="16.33203125" style="1"/>
+    <col min="7" max="7" width="21" style="13" customWidth="1"/>
+    <col min="8" max="8" width="32.44140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="48.21875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="23.21875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="37" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="37" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C1" s="37">
         <f>MATCH(Meta.Features!$D$3,Meta.Features!$3:$3,0)</f>
         <v>4</v>
@@ -2726,9 +2827,12 @@
         <f>MATCH(Meta.Features!$K$3,Meta.Features!$3:$3,0)</f>
         <v>11</v>
       </c>
-      <c r="L1" s="38"/>
-    </row>
-    <row r="2" spans="1:17" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="37">
+        <v>12</v>
+      </c>
+      <c r="M1" s="38"/>
+    </row>
+    <row r="2" spans="1:18" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>46</v>
       </c>
@@ -2748,13 +2852,19 @@
         <v>46</v>
       </c>
       <c r="G2" s="34" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="H2" s="34" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" s="20" customFormat="1" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I2" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="20" customFormat="1" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
         <v>38</v>
       </c>
@@ -2773,14 +2883,18 @@
       <c r="F3" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="H3" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
+      <c r="I3" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>593</v>
+      </c>
       <c r="K3" s="21"/>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
@@ -2788,8 +2902,9 @@
       <c r="O3" s="21"/>
       <c r="P3" s="21"/>
       <c r="Q3" s="21"/>
-    </row>
-    <row r="4" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R3" s="21"/>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -2812,14 +2927,19 @@
         <f>VLOOKUP(B4,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="13" t="str">
+        <f>VLOOKUP(B4,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="I4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -2827,8 +2947,9 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R4" s="1"/>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>40</v>
       </c>
@@ -2851,14 +2972,19 @@
         <f>VLOOKUP(B5,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Interval</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="13" t="str">
+        <f>VLOOKUP(B5,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="I5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>592</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -2866,8 +2992,9 @@
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R5" s="1"/>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -2890,14 +3017,19 @@
         <f>VLOOKUP(B6,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="13" t="str">
+        <f>VLOOKUP(B6,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>TRUE</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+      <c r="I6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -2905,8 +3037,9 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-    </row>
-    <row r="7" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R6" s="1"/>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>40</v>
       </c>
@@ -2929,14 +3062,19 @@
         <f>VLOOKUP(B7,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="13" t="str">
+        <f>VLOOKUP(B7,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
+      <c r="I7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -2944,8 +3082,9 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="1"/>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>40</v>
       </c>
@@ -2968,14 +3107,19 @@
         <f>VLOOKUP(B8,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Interval</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="13" t="str">
+        <f>VLOOKUP(B8,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+      <c r="I8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>591</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -2983,8 +3127,9 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
-    </row>
-    <row r="9" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="1"/>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>40</v>
       </c>
@@ -3007,14 +3152,19 @@
         <f>VLOOKUP(B9,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="13" t="str">
+        <f>VLOOKUP(B9,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>TRUE</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+      <c r="I9" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -3022,8 +3172,9 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-    </row>
-    <row r="10" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R9" s="1"/>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
@@ -3046,14 +3197,19 @@
         <f>VLOOKUP(B10,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Binary</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="13" t="str">
+        <f>VLOOKUP(B10,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>TRUE</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
+      <c r="I10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -3061,8 +3217,9 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
-    </row>
-    <row r="11" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R10" s="1"/>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -3085,14 +3242,19 @@
         <f>VLOOKUP(B11,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Interval</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="13" t="str">
+        <f>VLOOKUP(B11,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
+      <c r="I11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>591</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -3100,8 +3262,9 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-    </row>
-    <row r="12" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R11" s="1"/>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
@@ -3124,14 +3287,19 @@
         <f>VLOOKUP(B12,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="13" t="str">
+        <f>VLOOKUP(B12,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>TRUE</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="I12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -3139,8 +3307,9 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-    </row>
-    <row r="13" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R12" s="1"/>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>40</v>
       </c>
@@ -3163,14 +3332,19 @@
         <f>VLOOKUP(B13,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Ratio</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="13" t="str">
+        <f>VLOOKUP(B13,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
+      <c r="I13" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -3178,8 +3352,9 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-    </row>
-    <row r="14" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R13" s="1"/>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>40</v>
       </c>
@@ -3202,14 +3377,19 @@
         <f>VLOOKUP(B14,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="13" t="str">
+        <f>VLOOKUP(B14,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
+      <c r="I14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -3217,8 +3397,9 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-    </row>
-    <row r="15" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R14" s="1"/>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
@@ -3241,14 +3422,19 @@
         <f>VLOOKUP(B15,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Ratio</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="13" t="str">
+        <f>VLOOKUP(B15,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
+      <c r="I15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -3256,8 +3442,9 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
-    </row>
-    <row r="16" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R15" s="1"/>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
@@ -3280,14 +3467,19 @@
         <f>VLOOKUP(B16,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Ratio</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="13" t="str">
+        <f>VLOOKUP(B16,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
+      <c r="I16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -3295,8 +3487,9 @@
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
-    </row>
-    <row r="17" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R16" s="1"/>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
@@ -3319,14 +3512,19 @@
         <f>VLOOKUP(B17,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Ratio</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="13" t="str">
+        <f>VLOOKUP(B17,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
+      <c r="I17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -3334,8 +3532,9 @@
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
-    </row>
-    <row r="18" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R17" s="1"/>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
@@ -3358,14 +3557,19 @@
         <f>VLOOKUP(B18,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Interval</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="13" t="str">
+        <f>VLOOKUP(B18,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
+      <c r="I18" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -3373,8 +3577,9 @@
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
-    </row>
-    <row r="19" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R18" s="1"/>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
@@ -3397,14 +3602,19 @@
         <f>VLOOKUP(B19,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Ratio</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="13" t="str">
+        <f>VLOOKUP(B19,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
+      <c r="I19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -3412,8 +3622,9 @@
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
-    </row>
-    <row r="20" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R19" s="1"/>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
@@ -3436,14 +3647,19 @@
         <f>VLOOKUP(B20,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Interval</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="13" t="str">
+        <f>VLOOKUP(B20,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
+      <c r="I20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -3451,8 +3667,9 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-    </row>
-    <row r="21" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R20" s="1"/>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
@@ -3475,14 +3692,19 @@
         <f>VLOOKUP(B21,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Ratio</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="13" t="str">
+        <f>VLOOKUP(B21,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
+      <c r="I21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -3490,8 +3712,9 @@
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
-    </row>
-    <row r="22" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R21" s="1"/>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -3514,14 +3737,19 @@
         <f>VLOOKUP(B22,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Ratio</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="13" t="str">
+        <f>VLOOKUP(B22,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
+      <c r="I22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -3529,8 +3757,9 @@
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
-    </row>
-    <row r="23" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R22" s="1"/>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
@@ -3553,14 +3782,19 @@
         <f>VLOOKUP(B23,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="13" t="str">
+        <f>VLOOKUP(B23,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
+      <c r="I23" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -3568,8 +3802,9 @@
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
-    </row>
-    <row r="24" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R23" s="1"/>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -3592,14 +3827,19 @@
         <f>VLOOKUP(B24,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="13" t="str">
+        <f>VLOOKUP(B24,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
+      <c r="I24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -3607,8 +3847,9 @@
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
-    </row>
-    <row r="25" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R24" s="1"/>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
@@ -3631,14 +3872,19 @@
         <f>VLOOKUP(B25,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="13" t="str">
+        <f>VLOOKUP(B25,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>TRUE</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
+      <c r="I25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -3646,8 +3892,9 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
-    </row>
-    <row r="26" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>40</v>
       </c>
@@ -3670,14 +3917,19 @@
         <f>VLOOKUP(B26,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Interval</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="13" t="str">
+        <f>VLOOKUP(B26,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
+      <c r="I26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>591</v>
+      </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -3685,8 +3937,9 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
-    </row>
-    <row r="27" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>40</v>
       </c>
@@ -3709,14 +3962,19 @@
         <f>VLOOKUP(B27,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Interval</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="13" t="str">
+        <f>VLOOKUP(B27,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="I27" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>591</v>
+      </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -3724,8 +3982,9 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R27" s="1"/>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
@@ -3748,14 +4007,19 @@
         <f>VLOOKUP(B28,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Binary</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="13" t="str">
+        <f>VLOOKUP(B28,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>TRUE</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
+      <c r="I28" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -3763,8 +4027,9 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
-    </row>
-    <row r="29" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R28" s="1"/>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
@@ -3787,14 +4052,19 @@
         <f>VLOOKUP(B29,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Ratio</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="13" t="str">
+        <f>VLOOKUP(B29,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
+      <c r="I29" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -3802,8 +4072,9 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
-    </row>
-    <row r="30" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R29" s="1"/>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
@@ -3826,14 +4097,19 @@
         <f>VLOOKUP(B30,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="13" t="str">
+        <f>VLOOKUP(B30,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
+      <c r="I30" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -3841,8 +4117,9 @@
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
-    </row>
-    <row r="31" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R30" s="1"/>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
@@ -3865,14 +4142,19 @@
         <f>VLOOKUP(B31,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="13" t="str">
+        <f>VLOOKUP(B31,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
+      <c r="I31" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -3880,8 +4162,9 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
-    </row>
-    <row r="32" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R31" s="1"/>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>40</v>
       </c>
@@ -3904,14 +4187,19 @@
         <f>VLOOKUP(B32,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="13" t="str">
+        <f>VLOOKUP(B32,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>TRUE</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+      <c r="I32" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -3919,8 +4207,9 @@
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
-    </row>
-    <row r="33" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R32" s="1"/>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
@@ -3943,14 +4232,19 @@
         <f>VLOOKUP(B33,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="13" t="str">
+        <f>VLOOKUP(B33,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="I33" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -3958,8 +4252,9 @@
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
-    </row>
-    <row r="34" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R33" s="1"/>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
@@ -3982,14 +4277,19 @@
         <f>VLOOKUP(B34,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="13" t="str">
+        <f>VLOOKUP(B34,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="I34" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -3997,8 +4297,9 @@
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
-    </row>
-    <row r="35" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
@@ -4021,14 +4322,19 @@
         <f>VLOOKUP(B35,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="13" t="str">
+        <f>VLOOKUP(B35,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>TRUE</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
+      <c r="I35" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -4036,8 +4342,9 @@
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
-    </row>
-    <row r="36" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R35" s="1"/>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>40</v>
       </c>
@@ -4060,14 +4367,19 @@
         <f>VLOOKUP(B36,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="13" t="str">
+        <f>VLOOKUP(B36,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
+      <c r="I36" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -4075,8 +4387,9 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
-    </row>
-    <row r="37" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R36" s="1"/>
+    </row>
+    <row r="37" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>40</v>
       </c>
@@ -4099,14 +4412,19 @@
         <f>VLOOKUP(B37,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="13" t="str">
+        <f>VLOOKUP(B37,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>TRUE</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
+      <c r="I37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -4114,8 +4432,9 @@
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-    </row>
-    <row r="38" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -4138,14 +4457,19 @@
         <f>VLOOKUP(B38,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="13" t="str">
+        <f>VLOOKUP(B38,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
+      <c r="I38" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -4153,8 +4477,9 @@
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
-    </row>
-    <row r="39" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R38" s="1"/>
+    </row>
+    <row r="39" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>40</v>
       </c>
@@ -4177,14 +4502,19 @@
         <f>VLOOKUP(B39,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="13" t="str">
+        <f>VLOOKUP(B39,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
+      <c r="I39" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -4192,8 +4522,9 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
-    </row>
-    <row r="40" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R39" s="1"/>
+    </row>
+    <row r="40" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
@@ -4216,14 +4547,19 @@
         <f>VLOOKUP(B40,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="13" t="str">
+        <f>VLOOKUP(B40,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+      <c r="I40" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -4231,8 +4567,9 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
-    </row>
-    <row r="41" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R40" s="1"/>
+    </row>
+    <row r="41" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
@@ -4255,14 +4592,19 @@
         <f>VLOOKUP(B41,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="13" t="str">
+        <f>VLOOKUP(B41,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
+      <c r="I41" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -4270,8 +4612,9 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
-    </row>
-    <row r="42" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R41" s="1"/>
+    </row>
+    <row r="42" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>40</v>
       </c>
@@ -4294,14 +4637,19 @@
         <f>VLOOKUP(B42,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="13" t="str">
+        <f>VLOOKUP(B42,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+      <c r="I42" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -4309,8 +4657,9 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
-    </row>
-    <row r="43" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R42" s="1"/>
+    </row>
+    <row r="43" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>40</v>
       </c>
@@ -4333,14 +4682,19 @@
         <f>VLOOKUP(B43,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="13" t="str">
+        <f>VLOOKUP(B43,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
+      <c r="I43" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -4348,8 +4702,9 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
-    </row>
-    <row r="44" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R43" s="1"/>
+    </row>
+    <row r="44" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>40</v>
       </c>
@@ -4372,14 +4727,19 @@
         <f>VLOOKUP(B44,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="13" t="str">
+        <f>VLOOKUP(B44,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="I44" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -4387,8 +4747,9 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
-    </row>
-    <row r="45" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R44" s="1"/>
+    </row>
+    <row r="45" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
@@ -4411,14 +4772,19 @@
         <f>VLOOKUP(B45,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="13" t="str">
+        <f>VLOOKUP(B45,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
+      <c r="I45" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -4426,8 +4792,9 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
-    </row>
-    <row r="46" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R45" s="1"/>
+    </row>
+    <row r="46" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
@@ -4450,14 +4817,19 @@
         <f>VLOOKUP(B46,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Interval</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" s="13" t="str">
+        <f>VLOOKUP(B46,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>FALSE</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
+      <c r="I46" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>591</v>
+      </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -4465,8 +4837,9 @@
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
-    </row>
-    <row r="47" spans="1:17" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R46" s="1"/>
+    </row>
+    <row r="47" spans="1:18" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
@@ -4489,14 +4862,19 @@
         <f>VLOOKUP(B47,Meta.Features!$A:$K,$F$1,FALSE)</f>
         <v>Nominal</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="13" t="str">
+        <f>VLOOKUP(B47,Meta.Features!$A:$L,$G$1,FALSE)</f>
+        <v>TRUE</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
+      <c r="I47" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -4504,11 +4882,42 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G4:H47">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+  <conditionalFormatting sqref="H4:I47">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"Required"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+      <formula>"Required"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J11">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+      <formula>"Required"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J26">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+      <formula>"Required"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J27">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+      <formula>"Required"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J46">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+      <formula>"Required"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>"TRUE"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -4583,7 +4992,7 @@
         <v>37</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
@@ -5959,10 +6368,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E4:F47">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
       <formula>"FALSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
       <formula>"TRUE"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6071,10 +6480,10 @@
         <v>37</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G3" s="42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>88</v>
@@ -6092,10 +6501,10 @@
         <v>93</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O3" s="21"/>
       <c r="P3" s="21"/>
@@ -8392,10 +8801,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E4:G47">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"FALSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"TRUE"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8512,7 +8921,7 @@
         <v>AdmissionDate</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8531,7 +8940,7 @@
         <v>DischargeDate</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8550,7 +8959,7 @@
         <v>DischargeReasonCode</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8569,7 +8978,7 @@
         <v>DepartmentAdmissionDate</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8588,7 +8997,7 @@
         <v>DepartmentDischargeDate</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8607,7 +9016,7 @@
         <v>OPSDate</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -11600,12 +12009,12 @@
   <autoFilter ref="A3:S47" xr:uid="{AA71583B-5FBB-4A3B-81A2-9EC36E91DD0F}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="E4:E47">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"FALSE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:L47">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"TRUE"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11733,10 +12142,10 @@
         <v>37</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -11758,10 +12167,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>30</v>
@@ -11804,10 +12213,10 @@
         <v>2</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -11850,7 +12259,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>74</v>
@@ -11896,10 +12305,10 @@
         <v>4</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -11942,10 +12351,10 @@
         <v>5</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -11988,10 +12397,10 @@
         <v>6</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -12034,10 +12443,10 @@
         <v>7</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
@@ -12080,10 +12489,10 @@
         <v>8</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
@@ -12126,10 +12535,10 @@
         <v>9</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
@@ -12172,10 +12581,10 @@
         <v>10</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
@@ -12218,7 +12627,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>19</v>
@@ -12264,10 +12673,10 @@
         <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
@@ -12310,10 +12719,10 @@
         <v>13</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
@@ -12356,10 +12765,10 @@
         <v>14</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
@@ -12402,10 +12811,10 @@
         <v>15</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
@@ -12448,10 +12857,10 @@
         <v>16</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
@@ -12494,10 +12903,10 @@
         <v>17</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
@@ -12540,10 +12949,10 @@
         <v>18</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
@@ -12586,10 +12995,10 @@
         <v>19</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
@@ -12632,10 +13041,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
@@ -12678,10 +13087,10 @@
         <v>2</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
@@ -12724,10 +13133,10 @@
         <v>3</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
@@ -12770,10 +13179,10 @@
         <v>4</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
@@ -12816,10 +13225,10 @@
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
@@ -12862,10 +13271,10 @@
         <v>6</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
@@ -12908,10 +13317,10 @@
         <v>7</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
@@ -12954,10 +13363,10 @@
         <v>1</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>30</v>
@@ -13000,10 +13409,10 @@
         <v>2</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
@@ -13046,10 +13455,10 @@
         <v>3</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
@@ -13092,7 +13501,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>20</v>
@@ -13138,7 +13547,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>21</v>
@@ -13184,7 +13593,7 @@
         <v>6</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>36</v>
@@ -13230,10 +13639,10 @@
         <v>7</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
@@ -13276,10 +13685,10 @@
         <v>8</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
@@ -13322,10 +13731,10 @@
         <v>1</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>30</v>
@@ -13368,10 +13777,10 @@
         <v>2</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
@@ -13414,10 +13823,10 @@
         <v>3</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
@@ -13460,10 +13869,10 @@
         <v>4</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
@@ -13506,10 +13915,10 @@
         <v>1</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>30</v>
@@ -13552,10 +13961,10 @@
         <v>2</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
@@ -13644,7 +14053,7 @@
         <v>4</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>22</v>
@@ -13690,10 +14099,10 @@
         <v>5</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
@@ -13736,7 +14145,7 @@
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>36</v>
@@ -13765,15 +14174,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:N47">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"FALSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
       <formula>"TRUE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
       <formula>"Obligatory"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13914,7 +14323,7 @@
         <v>Nominal</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>1</v>
@@ -13982,7 +14391,7 @@
         <v>Nominal</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>0</v>
@@ -14016,7 +14425,7 @@
         <v>Nominal</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>6</v>
@@ -14056,10 +14465,10 @@
         <v>29</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J8" s="5"/>
     </row>
@@ -14090,10 +14499,10 @@
         <v>14</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J9" s="5"/>
     </row>
@@ -14124,10 +14533,10 @@
         <v>17</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J10" s="5"/>
     </row>
@@ -14158,10 +14567,10 @@
         <v>13</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J11" s="5"/>
     </row>
@@ -14192,10 +14601,10 @@
         <v>9</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J12" s="5"/>
     </row>
@@ -14226,10 +14635,10 @@
         <v>95</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J13" s="5"/>
     </row>
@@ -14254,16 +14663,16 @@
         <v>Nominal</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="J14" s="5"/>
     </row>
@@ -14294,10 +14703,10 @@
         <v>7</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J15" s="1"/>
     </row>
@@ -14380,16 +14789,16 @@
         <v>Nominal</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J18" s="1"/>
     </row>
@@ -14414,16 +14823,16 @@
         <v>Nominal</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J19" s="1"/>
     </row>
@@ -14448,16 +14857,16 @@
         <v>Nominal</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J20" s="1"/>
     </row>
@@ -14482,16 +14891,16 @@
         <v>Nominal</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J21" s="1"/>
     </row>
@@ -14516,16 +14925,16 @@
         <v>Nominal</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J22" s="1"/>
     </row>
@@ -14550,16 +14959,16 @@
         <v>Nominal</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J23" s="1"/>
     </row>
@@ -14584,16 +14993,16 @@
         <v>Nominal</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J24" s="1"/>
     </row>
@@ -14618,16 +15027,16 @@
         <v>Nominal</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J25" s="1"/>
     </row>
@@ -14652,16 +15061,16 @@
         <v>Nominal</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J26" s="1"/>
     </row>
@@ -14686,16 +15095,16 @@
         <v>Nominal</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J27" s="1"/>
     </row>
@@ -14720,16 +15129,16 @@
         <v>Nominal</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J28" s="1"/>
     </row>
@@ -14754,16 +15163,16 @@
         <v>Nominal</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J29" s="1"/>
     </row>
@@ -14788,16 +15197,16 @@
         <v>Nominal</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J30" s="1"/>
     </row>
@@ -14822,16 +15231,16 @@
         <v>Nominal</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J31" s="1"/>
     </row>
@@ -14856,16 +15265,16 @@
         <v>Nominal</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J32" s="1"/>
     </row>
@@ -14890,16 +15299,16 @@
         <v>Nominal</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J33" s="1"/>
     </row>
@@ -14924,16 +15333,16 @@
         <v>Nominal</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J34" s="1"/>
     </row>
@@ -14958,16 +15367,16 @@
         <v>Nominal</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J35" s="5"/>
     </row>
@@ -14992,16 +15401,16 @@
         <v>Nominal</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J36" s="5"/>
     </row>
@@ -15026,16 +15435,16 @@
         <v>Nominal</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J37" s="5"/>
     </row>
@@ -15060,16 +15469,16 @@
         <v>Nominal</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J38" s="5"/>
     </row>
@@ -15094,16 +15503,16 @@
         <v>Nominal</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J39" s="5"/>
     </row>
@@ -15128,16 +15537,16 @@
         <v>Nominal</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J40" s="5"/>
     </row>
@@ -15162,16 +15571,16 @@
         <v>Nominal</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J41" s="5"/>
     </row>
@@ -15196,16 +15605,16 @@
         <v>Nominal</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J42" s="5"/>
     </row>
@@ -15230,16 +15639,16 @@
         <v>Nominal</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J43" s="5"/>
     </row>
@@ -15264,16 +15673,16 @@
         <v>Nominal</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J44" s="5"/>
     </row>
@@ -15298,16 +15707,16 @@
         <v>Nominal</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J45" s="5"/>
     </row>
@@ -15332,16 +15741,16 @@
         <v>Nominal</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J46" s="5"/>
     </row>
@@ -15366,16 +15775,16 @@
         <v>Nominal</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J47" s="5"/>
     </row>
@@ -15400,16 +15809,16 @@
         <v>Nominal</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J48" s="5"/>
     </row>
@@ -15434,16 +15843,16 @@
         <v>Nominal</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J49" s="5"/>
     </row>
@@ -15468,16 +15877,16 @@
         <v>Nominal</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J50" s="5"/>
     </row>
@@ -15502,16 +15911,16 @@
         <v>Nominal</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J51" s="1"/>
     </row>
@@ -15536,16 +15945,16 @@
         <v>Nominal</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J52" s="1"/>
     </row>
@@ -15570,16 +15979,16 @@
         <v>Nominal</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J53" s="1"/>
     </row>
@@ -15604,16 +16013,16 @@
         <v>Nominal</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J54" s="1"/>
     </row>
@@ -15638,16 +16047,16 @@
         <v>Nominal</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -15671,16 +16080,16 @@
         <v>Nominal</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -15704,16 +16113,16 @@
         <v>Nominal</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -15737,16 +16146,16 @@
         <v>Nominal</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -15770,16 +16179,16 @@
         <v>Nominal</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -15803,16 +16212,16 @@
         <v>Nominal</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -15836,16 +16245,16 @@
         <v>Nominal</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J61" s="1"/>
     </row>
@@ -15870,16 +16279,16 @@
         <v>Nominal</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J62" s="1"/>
     </row>
@@ -15904,16 +16313,16 @@
         <v>Nominal</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J63" s="1"/>
     </row>
@@ -15938,16 +16347,16 @@
         <v>Nominal</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J64" s="1"/>
     </row>
@@ -15972,16 +16381,16 @@
         <v>Nominal</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J65" s="1"/>
     </row>
@@ -16006,16 +16415,16 @@
         <v>Nominal</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J66" s="1"/>
     </row>
@@ -16040,16 +16449,16 @@
         <v>Nominal</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J67" s="1"/>
     </row>
@@ -16074,16 +16483,16 @@
         <v>Nominal</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16107,16 +16516,16 @@
         <v>Nominal</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16140,16 +16549,16 @@
         <v>Nominal</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16173,16 +16582,16 @@
         <v>Nominal</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16206,16 +16615,16 @@
         <v>Nominal</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16239,16 +16648,16 @@
         <v>Nominal</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16272,16 +16681,16 @@
         <v>Nominal</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16305,16 +16714,16 @@
         <v>Nominal</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16338,16 +16747,16 @@
         <v>Nominal</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16371,16 +16780,16 @@
         <v>Nominal</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16404,16 +16813,16 @@
         <v>Nominal</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16437,16 +16846,16 @@
         <v>Nominal</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16470,16 +16879,16 @@
         <v>Nominal</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16503,16 +16912,16 @@
         <v>Nominal</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16536,16 +16945,16 @@
         <v>Nominal</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16569,16 +16978,16 @@
         <v>Nominal</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -16602,16 +17011,16 @@
         <v>Nominal</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J84" s="5"/>
     </row>
@@ -16636,16 +17045,16 @@
         <v>Nominal</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J85" s="5"/>
     </row>
@@ -16670,16 +17079,16 @@
         <v>Nominal</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J86" s="5"/>
     </row>
@@ -16704,16 +17113,16 @@
         <v>Nominal</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J87" s="5"/>
     </row>
@@ -16738,16 +17147,16 @@
         <v>Nominal</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J88" s="5"/>
     </row>
@@ -16772,16 +17181,16 @@
         <v>Nominal</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J89" s="5"/>
     </row>
@@ -16806,16 +17215,16 @@
         <v>Nominal</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J90" s="5"/>
     </row>
@@ -16840,16 +17249,16 @@
         <v>Nominal</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J91" s="5"/>
     </row>
@@ -16874,16 +17283,16 @@
         <v>Nominal</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J92" s="5"/>
     </row>
@@ -16908,16 +17317,16 @@
         <v>Nominal</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J93" s="5"/>
     </row>
@@ -16942,16 +17351,16 @@
         <v>Nominal</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J94" s="5"/>
     </row>
@@ -16976,16 +17385,16 @@
         <v>Nominal</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J95" s="5"/>
     </row>
@@ -17010,16 +17419,16 @@
         <v>Nominal</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J96" s="5"/>
     </row>
@@ -17044,16 +17453,16 @@
         <v>Nominal</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J97" s="5"/>
     </row>
@@ -17078,16 +17487,16 @@
         <v>Nominal</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J98" s="5"/>
     </row>
@@ -17112,16 +17521,16 @@
         <v>Nominal</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J99" s="1"/>
     </row>
@@ -17146,16 +17555,16 @@
         <v>Nominal</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J100" s="1"/>
     </row>
@@ -17180,16 +17589,16 @@
         <v>Nominal</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J101" s="1"/>
     </row>
@@ -17214,16 +17623,16 @@
         <v>Nominal</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J102" s="1"/>
     </row>
@@ -17248,16 +17657,16 @@
         <v>Nominal</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J103" s="1"/>
     </row>
@@ -17282,16 +17691,16 @@
         <v>Nominal</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17315,16 +17724,16 @@
         <v>Nominal</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17348,16 +17757,16 @@
         <v>Nominal</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17381,16 +17790,16 @@
         <v>Nominal</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17414,16 +17823,16 @@
         <v>Nominal</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17447,16 +17856,16 @@
         <v>Nominal</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17480,16 +17889,16 @@
         <v>Nominal</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17513,16 +17922,16 @@
         <v>Nominal</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17546,16 +17955,16 @@
         <v>Nominal</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17579,16 +17988,16 @@
         <v>Nominal</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17612,16 +18021,16 @@
         <v>Nominal</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17645,16 +18054,16 @@
         <v>Nominal</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17678,16 +18087,16 @@
         <v>Nominal</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H116" s="7" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17711,16 +18120,16 @@
         <v>Nominal</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17744,16 +18153,16 @@
         <v>Nominal</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H118" s="7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17777,16 +18186,16 @@
         <v>Nominal</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H119" s="7" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I119" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17810,16 +18219,16 @@
         <v>Nominal</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H120" s="7" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I120" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17843,16 +18252,16 @@
         <v>Nominal</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H121" s="7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17876,16 +18285,16 @@
         <v>Nominal</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H122" s="7" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I122" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17909,16 +18318,16 @@
         <v>Nominal</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I123" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17942,16 +18351,16 @@
         <v>Nominal</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H124" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="I124" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -17975,16 +18384,16 @@
         <v>Nominal</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H125" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18008,16 +18417,16 @@
         <v>Nominal</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H126" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I126" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18041,16 +18450,16 @@
         <v>Nominal</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H127" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18074,16 +18483,16 @@
         <v>Nominal</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H128" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I128" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18107,16 +18516,16 @@
         <v>Nominal</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18140,16 +18549,16 @@
         <v>Nominal</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18173,16 +18582,16 @@
         <v>Nominal</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18206,16 +18615,16 @@
         <v>Nominal</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18239,16 +18648,16 @@
         <v>Nominal</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18272,16 +18681,16 @@
         <v>Nominal</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18305,16 +18714,16 @@
         <v>Nominal</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H135" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18338,16 +18747,16 @@
         <v>Nominal</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18371,16 +18780,16 @@
         <v>Nominal</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H137" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18404,16 +18813,16 @@
         <v>Nominal</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18437,16 +18846,16 @@
         <v>Nominal</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H139" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18470,16 +18879,16 @@
         <v>Nominal</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H140" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18503,16 +18912,16 @@
         <v>Nominal</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I141" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18536,16 +18945,16 @@
         <v>Nominal</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H142" s="7" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="I142" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18569,16 +18978,16 @@
         <v>Nominal</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H143" s="7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18602,16 +19011,16 @@
         <v>Nominal</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H144" s="7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I144" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18635,16 +19044,16 @@
         <v>Nominal</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I145" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18668,16 +19077,16 @@
         <v>Nominal</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="I146" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18701,16 +19110,16 @@
         <v>Nominal</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I147" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18734,16 +19143,16 @@
         <v>Nominal</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="I148" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18767,16 +19176,16 @@
         <v>Nominal</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="I149" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18800,16 +19209,16 @@
         <v>Nominal</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I150" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18833,16 +19242,16 @@
         <v>Nominal</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I151" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18866,16 +19275,16 @@
         <v>Nominal</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I152" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18899,16 +19308,16 @@
         <v>Nominal</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18932,16 +19341,16 @@
         <v>Nominal</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I154" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -18965,16 +19374,16 @@
         <v>Nominal</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J155" s="1"/>
     </row>
@@ -18999,16 +19408,16 @@
         <v>Nominal</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J156" s="1"/>
     </row>
@@ -19033,16 +19442,16 @@
         <v>Nominal</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J157" s="1"/>
     </row>
@@ -19067,16 +19476,16 @@
         <v>Nominal</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="J158" s="1"/>
     </row>
@@ -19101,16 +19510,16 @@
         <v>Nominal</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="J159" s="1"/>
     </row>
@@ -19135,16 +19544,16 @@
         <v>Nominal</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="J160" s="1"/>
     </row>
@@ -19169,16 +19578,16 @@
         <v>Nominal</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J161" s="1"/>
     </row>
@@ -19203,16 +19612,16 @@
         <v>Nominal</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="J162" s="1"/>
     </row>
@@ -19237,16 +19646,16 @@
         <v>Nominal</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="J163" s="1"/>
     </row>
@@ -19271,16 +19680,16 @@
         <v>Nominal</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="J164" s="1"/>
     </row>
@@ -19305,16 +19714,16 @@
         <v>Nominal</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="J165" s="1"/>
     </row>
@@ -19339,16 +19748,16 @@
         <v>Nominal</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="J166" s="1"/>
     </row>
@@ -19373,16 +19782,16 @@
         <v>Nominal</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J167" s="1"/>
     </row>
@@ -19407,16 +19816,16 @@
         <v>Nominal</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J168" s="1"/>
     </row>
@@ -19441,16 +19850,16 @@
         <v>Nominal</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J169" s="1"/>
     </row>
@@ -19475,16 +19884,16 @@
         <v>Nominal</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="J170" s="1"/>
     </row>
@@ -19509,16 +19918,16 @@
         <v>Nominal</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="J171" s="1"/>
     </row>
@@ -19543,16 +19952,16 @@
         <v>Nominal</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="J172" s="1"/>
     </row>
@@ -19577,16 +19986,16 @@
         <v>Nominal</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J173" s="1"/>
     </row>
@@ -19611,16 +20020,16 @@
         <v>Nominal</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="J174" s="1"/>
     </row>
@@ -19645,16 +20054,16 @@
         <v>Nominal</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J175" s="1"/>
     </row>
@@ -19679,16 +20088,16 @@
         <v>Nominal</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J176" s="1"/>
     </row>
@@ -19713,16 +20122,16 @@
         <v>Nominal</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J177" s="1"/>
     </row>
@@ -19747,16 +20156,16 @@
         <v>Nominal</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J178" s="1"/>
     </row>
@@ -19781,16 +20190,16 @@
         <v>Nominal</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="J179" s="1"/>
     </row>
@@ -19815,16 +20224,16 @@
         <v>Nominal</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J180" s="1"/>
     </row>
@@ -19849,16 +20258,16 @@
         <v>Nominal</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="J181" s="1"/>
     </row>
@@ -19883,16 +20292,16 @@
         <v>Nominal</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="J182" s="1"/>
     </row>
@@ -19917,16 +20326,16 @@
         <v>Nominal</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="J183" s="1"/>
     </row>
@@ -19951,16 +20360,16 @@
         <v>Nominal</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="J184" s="1"/>
     </row>
@@ -19985,16 +20394,16 @@
         <v>Nominal</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="J185" s="1"/>
     </row>
@@ -20019,16 +20428,16 @@
         <v>Nominal</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="J186" s="1"/>
     </row>
@@ -20053,16 +20462,16 @@
         <v>Nominal</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="J187" s="1"/>
     </row>
@@ -20087,16 +20496,16 @@
         <v>Nominal</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J188" s="1"/>
     </row>
@@ -20121,16 +20530,16 @@
         <v>Nominal</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J189" s="1"/>
     </row>
@@ -20155,16 +20564,16 @@
         <v>Nominal</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J190" s="1"/>
     </row>
@@ -20189,16 +20598,16 @@
         <v>Nominal</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="J191" s="1"/>
     </row>
@@ -20223,16 +20632,16 @@
         <v>Nominal</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="J192" s="1"/>
     </row>
@@ -20257,16 +20666,16 @@
         <v>Nominal</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="J193" s="1"/>
     </row>
@@ -20291,16 +20700,16 @@
         <v>Nominal</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J194" s="1"/>
     </row>
@@ -20325,16 +20734,16 @@
         <v>Nominal</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="J195" s="1"/>
     </row>
@@ -20359,16 +20768,16 @@
         <v>Nominal</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="J196" s="1"/>
     </row>
@@ -20393,16 +20802,16 @@
         <v>Nominal</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="J197" s="1"/>
     </row>
@@ -20427,16 +20836,16 @@
         <v>Nominal</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="J198" s="1"/>
     </row>
@@ -20461,16 +20870,16 @@
         <v>Nominal</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="J199" s="1"/>
     </row>
@@ -20553,16 +20962,16 @@
         <v>Nominal</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="J202" s="1"/>
     </row>
@@ -20587,16 +20996,16 @@
         <v>Nominal</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="J203" s="1"/>
     </row>
@@ -20864,17 +21273,17 @@
   </sheetData>
   <autoFilter ref="A3:K212" xr:uid="{6EF1C1D3-3AE0-4822-BECE-5F11FDFA805B}"/>
   <conditionalFormatting sqref="F4:F212">
-    <cfRule type="expression" dxfId="9" priority="129">
+    <cfRule type="expression" dxfId="22" priority="129">
       <formula>($F4&lt;&gt;$G4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G212">
-    <cfRule type="expression" dxfId="8" priority="120">
+    <cfRule type="expression" dxfId="21" priority="120">
       <formula>($F4&lt;&gt;$G4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G145:G154">
-    <cfRule type="expression" dxfId="7" priority="37">
+    <cfRule type="expression" dxfId="20" priority="37">
       <formula>($F145&lt;&gt;$G145)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21096,22 +21505,22 @@
         <v>24</v>
       </c>
       <c r="D3" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>113</v>
-      </c>
       <c r="F3" s="19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J3" s="21"/>
       <c r="K3" s="21"/>
@@ -21125,7 +21534,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>30</v>
@@ -21394,10 +21803,10 @@
         <v>24</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>101</v>
@@ -21415,10 +21824,10 @@
         <v>105</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>106</v>
+        <v>589</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>107</v>
+        <v>590</v>
       </c>
       <c r="M3" s="21"/>
       <c r="N3" s="21"/>
@@ -21438,7 +21847,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>31</v>
@@ -21797,10 +22206,10 @@
         <v>24</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>101</v>
@@ -21818,10 +22227,10 @@
         <v>105</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>106</v>
+        <v>589</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>107</v>
+        <v>590</v>
       </c>
       <c r="M3" s="21"/>
       <c r="N3" s="21"/>
@@ -21841,7 +22250,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>31</v>
@@ -22173,10 +22582,10 @@
         <v>24</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
